--- a/docs/test scenario.xlsx
+++ b/docs/test scenario.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Modul</t>
   </si>
@@ -72,9 +72,6 @@
     <t>TS15</t>
   </si>
   <si>
-    <t>TS16</t>
-  </si>
-  <si>
     <t>Proveriti da li svi navigacioni linkovi postoje u meniju i vode na ispravne URL adrese</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
   </si>
   <si>
     <t>Proveriti da li galerija sadrži vidljive slike</t>
-  </si>
-  <si>
-    <t>Proveriti da li su usluge salona prikazane na naslovnoj strani</t>
   </si>
   <si>
     <t>Proveriti da li postoji link ka Facebook stranici salona</t>
@@ -145,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +177,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -289,17 +298,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -334,6 +332,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -341,32 +354,17 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -376,14 +374,20 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -698,187 +702,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10"/>
+      <c r="B4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="6" t="s">
+    <row r="17" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
+    <row r="18" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
